--- a/transport/trans_config.xlsx
+++ b/transport/trans_config.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fraunhofer-my.sharepoint.com/personal/rakesh_etikala_narendar_iee_fraunhofer_de/Documents/Desktop/sectoral-energy-demands/transport/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="175" documentId="11_23F921EDAE034F2B492C4C492D40CC9F4213A6C0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AFAB7FE-AB25-44FA-A8DE-19F29CA6B255}"/>
+  <xr:revisionPtr revIDLastSave="205" documentId="11_23F921EDAE034F2B492C4C492D40CC9F4213A6C0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3458ECFF-A4F2-48C7-972E-731BE5BA7BAD}"/>
   <bookViews>
-    <workbookView xWindow="19720" yWindow="1980" windowWidth="18450" windowHeight="13730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19910" yWindow="1770" windowWidth="18450" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2016" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2052" uniqueCount="166">
   <si>
     <t>Assumption Type</t>
   </si>
@@ -513,6 +526,12 @@
   <si>
     <t>Final Energy Intensity - FCEV Freight Ship</t>
   </si>
+  <si>
+    <t>Total Energy - Int. Maritime</t>
+  </si>
+  <si>
+    <t>Total Energy - Int. Aviation</t>
+  </si>
 </sst>
 </file>
 
@@ -879,7 +898,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BT649"/>
+  <dimension ref="A1:BT661"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.36328125" bestFit="1" customWidth="1"/>
@@ -50148,10 +50167,10 @@
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B422" t="s">
-        <v>121</v>
+        <v>164</v>
       </c>
       <c r="C422">
         <v>2030</v>
@@ -50160,15 +50179,15 @@
         <v>159</v>
       </c>
       <c r="E422">
-        <v>0.16700000000000001</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B423" t="s">
-        <v>121</v>
+        <v>164</v>
       </c>
       <c r="C423">
         <v>2030</v>
@@ -50177,15 +50196,15 @@
         <v>160</v>
       </c>
       <c r="E423">
-        <v>0.68</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B424" t="s">
-        <v>121</v>
+        <v>164</v>
       </c>
       <c r="C424">
         <v>2030</v>
@@ -50194,15 +50213,15 @@
         <v>161</v>
       </c>
       <c r="E424">
-        <v>0.68</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B425" t="s">
-        <v>121</v>
+        <v>164</v>
       </c>
       <c r="C425">
         <v>2050</v>
@@ -50211,15 +50230,15 @@
         <v>159</v>
       </c>
       <c r="E425">
-        <v>0.16700000000000001</v>
+        <v>1.7000000000000001E-2</v>
       </c>
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B426" t="s">
-        <v>121</v>
+        <v>164</v>
       </c>
       <c r="C426">
         <v>2050</v>
@@ -50228,15 +50247,15 @@
         <v>160</v>
       </c>
       <c r="E426">
-        <v>0.08</v>
+        <v>1.7000000000000001E-2</v>
       </c>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B427" t="s">
-        <v>121</v>
+        <v>164</v>
       </c>
       <c r="C427">
         <v>2050</v>
@@ -50245,15 +50264,15 @@
         <v>161</v>
       </c>
       <c r="E427">
-        <v>0.03</v>
+        <v>1.7000000000000001E-2</v>
       </c>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B428" t="s">
-        <v>122</v>
+        <v>165</v>
       </c>
       <c r="C428">
         <v>2030</v>
@@ -50262,15 +50281,15 @@
         <v>159</v>
       </c>
       <c r="E428">
-        <v>0.83299999999999996</v>
+        <v>2.9700000000000001E-2</v>
       </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B429" t="s">
-        <v>122</v>
+        <v>165</v>
       </c>
       <c r="C429">
         <v>2030</v>
@@ -50279,15 +50298,15 @@
         <v>160</v>
       </c>
       <c r="E429">
-        <v>0.25</v>
+        <v>2.9700000000000001E-2</v>
       </c>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B430" t="s">
-        <v>122</v>
+        <v>165</v>
       </c>
       <c r="C430">
         <v>2030</v>
@@ -50296,15 +50315,15 @@
         <v>161</v>
       </c>
       <c r="E430">
-        <v>0.2</v>
+        <v>2.9700000000000001E-2</v>
       </c>
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B431" t="s">
-        <v>122</v>
+        <v>165</v>
       </c>
       <c r="C431">
         <v>2050</v>
@@ -50313,15 +50332,15 @@
         <v>159</v>
       </c>
       <c r="E431">
-        <v>0.83299999999999996</v>
+        <v>3.0700000000000002E-2</v>
       </c>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B432" t="s">
-        <v>122</v>
+        <v>165</v>
       </c>
       <c r="C432">
         <v>2050</v>
@@ -50330,15 +50349,15 @@
         <v>160</v>
       </c>
       <c r="E432">
-        <v>0.1</v>
+        <v>3.0700000000000002E-2</v>
       </c>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B433" t="s">
-        <v>122</v>
+        <v>165</v>
       </c>
       <c r="C433">
         <v>2050</v>
@@ -50347,7 +50366,7 @@
         <v>161</v>
       </c>
       <c r="E433">
-        <v>0.1</v>
+        <v>3.0700000000000002E-2</v>
       </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.35">
@@ -50355,16 +50374,16 @@
         <v>73</v>
       </c>
       <c r="B434" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C434">
-        <v>2030</v>
+        <v>2050</v>
       </c>
       <c r="D434" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E434">
-        <v>0</v>
+        <v>0.16700000000000001</v>
       </c>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.35">
@@ -50372,7 +50391,7 @@
         <v>73</v>
       </c>
       <c r="B435" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C435">
         <v>2030</v>
@@ -50381,7 +50400,7 @@
         <v>160</v>
       </c>
       <c r="E435">
-        <v>0</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.35">
@@ -50389,7 +50408,7 @@
         <v>73</v>
       </c>
       <c r="B436" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C436">
         <v>2030</v>
@@ -50398,7 +50417,7 @@
         <v>161</v>
       </c>
       <c r="E436">
-        <v>0</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.35">
@@ -50406,7 +50425,7 @@
         <v>73</v>
       </c>
       <c r="B437" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C437">
         <v>2050</v>
@@ -50415,7 +50434,7 @@
         <v>159</v>
       </c>
       <c r="E437">
-        <v>0</v>
+        <v>0.16700000000000001</v>
       </c>
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.35">
@@ -50423,7 +50442,7 @@
         <v>73</v>
       </c>
       <c r="B438" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C438">
         <v>2050</v>
@@ -50432,7 +50451,7 @@
         <v>160</v>
       </c>
       <c r="E438">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.35">
@@ -50440,7 +50459,7 @@
         <v>73</v>
       </c>
       <c r="B439" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C439">
         <v>2050</v>
@@ -50449,7 +50468,7 @@
         <v>161</v>
       </c>
       <c r="E439">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.35">
@@ -50457,7 +50476,7 @@
         <v>73</v>
       </c>
       <c r="B440" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C440">
         <v>2030</v>
@@ -50466,7 +50485,7 @@
         <v>159</v>
       </c>
       <c r="E440">
-        <v>0</v>
+        <v>0.83299999999999996</v>
       </c>
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.35">
@@ -50474,7 +50493,7 @@
         <v>73</v>
       </c>
       <c r="B441" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C441">
         <v>2030</v>
@@ -50483,7 +50502,7 @@
         <v>160</v>
       </c>
       <c r="E441">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.35">
@@ -50491,7 +50510,7 @@
         <v>73</v>
       </c>
       <c r="B442" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C442">
         <v>2030</v>
@@ -50500,7 +50519,7 @@
         <v>161</v>
       </c>
       <c r="E442">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.35">
@@ -50508,7 +50527,7 @@
         <v>73</v>
       </c>
       <c r="B443" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C443">
         <v>2050</v>
@@ -50517,7 +50536,7 @@
         <v>159</v>
       </c>
       <c r="E443">
-        <v>0</v>
+        <v>0.83299999999999996</v>
       </c>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.35">
@@ -50525,7 +50544,7 @@
         <v>73</v>
       </c>
       <c r="B444" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C444">
         <v>2050</v>
@@ -50534,7 +50553,7 @@
         <v>160</v>
       </c>
       <c r="E444">
-        <v>0.75</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.35">
@@ -50542,7 +50561,7 @@
         <v>73</v>
       </c>
       <c r="B445" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C445">
         <v>2050</v>
@@ -50551,7 +50570,7 @@
         <v>161</v>
       </c>
       <c r="E445">
-        <v>0.96</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.35">
@@ -50559,7 +50578,7 @@
         <v>73</v>
       </c>
       <c r="B446" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C446">
         <v>2030</v>
@@ -50576,7 +50595,7 @@
         <v>73</v>
       </c>
       <c r="B447" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C447">
         <v>2030</v>
@@ -50585,7 +50604,7 @@
         <v>160</v>
       </c>
       <c r="E447">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.35">
@@ -50593,7 +50612,7 @@
         <v>73</v>
       </c>
       <c r="B448" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C448">
         <v>2030</v>
@@ -50610,7 +50629,7 @@
         <v>73</v>
       </c>
       <c r="B449" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C449">
         <v>2050</v>
@@ -50627,7 +50646,7 @@
         <v>73</v>
       </c>
       <c r="B450" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C450">
         <v>2050</v>
@@ -50636,7 +50655,7 @@
         <v>160</v>
       </c>
       <c r="E450">
-        <v>7.0000000000000007E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.35">
@@ -50644,7 +50663,7 @@
         <v>73</v>
       </c>
       <c r="B451" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C451">
         <v>2050</v>
@@ -50661,7 +50680,7 @@
         <v>73</v>
       </c>
       <c r="B452" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C452">
         <v>2030</v>
@@ -50670,7 +50689,7 @@
         <v>159</v>
       </c>
       <c r="E452">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.35">
@@ -50678,7 +50697,7 @@
         <v>73</v>
       </c>
       <c r="B453" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C453">
         <v>2030</v>
@@ -50687,7 +50706,7 @@
         <v>160</v>
       </c>
       <c r="E453">
-        <v>0.93</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.35">
@@ -50695,7 +50714,7 @@
         <v>73</v>
       </c>
       <c r="B454" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C454">
         <v>2030</v>
@@ -50704,7 +50723,7 @@
         <v>161</v>
       </c>
       <c r="E454">
-        <v>0.88</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.35">
@@ -50712,7 +50731,7 @@
         <v>73</v>
       </c>
       <c r="B455" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C455">
         <v>2050</v>
@@ -50721,7 +50740,7 @@
         <v>159</v>
       </c>
       <c r="E455">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.35">
@@ -50729,7 +50748,7 @@
         <v>73</v>
       </c>
       <c r="B456" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C456">
         <v>2050</v>
@@ -50738,7 +50757,7 @@
         <v>160</v>
       </c>
       <c r="E456">
-        <v>0.18</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.35">
@@ -50746,7 +50765,7 @@
         <v>73</v>
       </c>
       <c r="B457" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C457">
         <v>2050</v>
@@ -50755,7 +50774,7 @@
         <v>161</v>
       </c>
       <c r="E457">
-        <v>0.04</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.35">
@@ -50763,7 +50782,7 @@
         <v>73</v>
       </c>
       <c r="B458" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C458">
         <v>2030</v>
@@ -50780,7 +50799,7 @@
         <v>73</v>
       </c>
       <c r="B459" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C459">
         <v>2030</v>
@@ -50789,7 +50808,7 @@
         <v>160</v>
       </c>
       <c r="E459">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.35">
@@ -50797,7 +50816,7 @@
         <v>73</v>
       </c>
       <c r="B460" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C460">
         <v>2030</v>
@@ -50806,7 +50825,7 @@
         <v>161</v>
       </c>
       <c r="E460">
-        <v>0.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.35">
@@ -50814,7 +50833,7 @@
         <v>73</v>
       </c>
       <c r="B461" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C461">
         <v>2050</v>
@@ -50831,7 +50850,7 @@
         <v>73</v>
       </c>
       <c r="B462" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C462">
         <v>2050</v>
@@ -50840,7 +50859,7 @@
         <v>160</v>
       </c>
       <c r="E462">
-        <v>0.75</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.35">
@@ -50848,7 +50867,7 @@
         <v>73</v>
       </c>
       <c r="B463" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C463">
         <v>2050</v>
@@ -50857,7 +50876,7 @@
         <v>161</v>
       </c>
       <c r="E463">
-        <v>0.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.35">
@@ -50865,7 +50884,7 @@
         <v>73</v>
       </c>
       <c r="B464" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C464">
         <v>2030</v>
@@ -50874,7 +50893,7 @@
         <v>159</v>
       </c>
       <c r="E464">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.35">
@@ -50882,7 +50901,7 @@
         <v>73</v>
       </c>
       <c r="B465" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C465">
         <v>2030</v>
@@ -50891,7 +50910,7 @@
         <v>160</v>
       </c>
       <c r="E465">
-        <v>0.01</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.35">
@@ -50899,7 +50918,7 @@
         <v>73</v>
       </c>
       <c r="B466" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C466">
         <v>2030</v>
@@ -50908,7 +50927,7 @@
         <v>161</v>
       </c>
       <c r="E466">
-        <v>0</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.35">
@@ -50916,7 +50935,7 @@
         <v>73</v>
       </c>
       <c r="B467" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C467">
         <v>2050</v>
@@ -50925,7 +50944,7 @@
         <v>159</v>
       </c>
       <c r="E467">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.35">
@@ -50933,7 +50952,7 @@
         <v>73</v>
       </c>
       <c r="B468" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C468">
         <v>2050</v>
@@ -50942,7 +50961,7 @@
         <v>160</v>
       </c>
       <c r="E468">
-        <v>7.0000000000000007E-2</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.35">
@@ -50950,7 +50969,7 @@
         <v>73</v>
       </c>
       <c r="B469" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C469">
         <v>2050</v>
@@ -50959,7 +50978,7 @@
         <v>161</v>
       </c>
       <c r="E469">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.35">
@@ -50967,7 +50986,7 @@
         <v>73</v>
       </c>
       <c r="B470" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C470">
         <v>2030</v>
@@ -50976,7 +50995,7 @@
         <v>159</v>
       </c>
       <c r="E470">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.35">
@@ -50984,7 +51003,7 @@
         <v>73</v>
       </c>
       <c r="B471" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C471">
         <v>2030</v>
@@ -50993,7 +51012,7 @@
         <v>160</v>
       </c>
       <c r="E471">
-        <v>0.94</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.35">
@@ -51001,7 +51020,7 @@
         <v>73</v>
       </c>
       <c r="B472" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C472">
         <v>2030</v>
@@ -51010,7 +51029,7 @@
         <v>161</v>
       </c>
       <c r="E472">
-        <v>0.88</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.35">
@@ -51018,7 +51037,7 @@
         <v>73</v>
       </c>
       <c r="B473" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C473">
         <v>2050</v>
@@ -51027,7 +51046,7 @@
         <v>159</v>
       </c>
       <c r="E473">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.35">
@@ -51035,7 +51054,7 @@
         <v>73</v>
       </c>
       <c r="B474" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C474">
         <v>2050</v>
@@ -51044,7 +51063,7 @@
         <v>160</v>
       </c>
       <c r="E474">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.35">
@@ -51052,7 +51071,7 @@
         <v>73</v>
       </c>
       <c r="B475" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C475">
         <v>2050</v>
@@ -51061,7 +51080,7 @@
         <v>161</v>
       </c>
       <c r="E475">
-        <v>0.1</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.35">
@@ -51069,7 +51088,7 @@
         <v>73</v>
       </c>
       <c r="B476" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C476">
         <v>2030</v>
@@ -51086,7 +51105,7 @@
         <v>73</v>
       </c>
       <c r="B477" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C477">
         <v>2030</v>
@@ -51095,7 +51114,7 @@
         <v>160</v>
       </c>
       <c r="E477">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.35">
@@ -51103,7 +51122,7 @@
         <v>73</v>
       </c>
       <c r="B478" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C478">
         <v>2030</v>
@@ -51112,7 +51131,7 @@
         <v>161</v>
       </c>
       <c r="E478">
-        <v>0.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.35">
@@ -51120,7 +51139,7 @@
         <v>73</v>
       </c>
       <c r="B479" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C479">
         <v>2050</v>
@@ -51137,7 +51156,7 @@
         <v>73</v>
       </c>
       <c r="B480" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C480">
         <v>2050</v>
@@ -51146,7 +51165,7 @@
         <v>160</v>
       </c>
       <c r="E480">
-        <v>0.8</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.35">
@@ -51154,7 +51173,7 @@
         <v>73</v>
       </c>
       <c r="B481" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C481">
         <v>2050</v>
@@ -51163,7 +51182,7 @@
         <v>161</v>
       </c>
       <c r="E481">
-        <v>0.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.35">
@@ -51171,7 +51190,7 @@
         <v>73</v>
       </c>
       <c r="B482" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C482">
         <v>2030</v>
@@ -51180,7 +51199,7 @@
         <v>159</v>
       </c>
       <c r="E482">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.35">
@@ -51188,7 +51207,7 @@
         <v>73</v>
       </c>
       <c r="B483" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C483">
         <v>2030</v>
@@ -51197,7 +51216,7 @@
         <v>160</v>
       </c>
       <c r="E483">
-        <v>0</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.35">
@@ -51205,7 +51224,7 @@
         <v>73</v>
       </c>
       <c r="B484" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C484">
         <v>2030</v>
@@ -51214,7 +51233,7 @@
         <v>161</v>
       </c>
       <c r="E484">
-        <v>0</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.35">
@@ -51222,7 +51241,7 @@
         <v>73</v>
       </c>
       <c r="B485" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C485">
         <v>2050</v>
@@ -51231,7 +51250,7 @@
         <v>159</v>
       </c>
       <c r="E485">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.35">
@@ -51239,7 +51258,7 @@
         <v>73</v>
       </c>
       <c r="B486" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C486">
         <v>2050</v>
@@ -51248,7 +51267,7 @@
         <v>160</v>
       </c>
       <c r="E486">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.35">
@@ -51256,7 +51275,7 @@
         <v>73</v>
       </c>
       <c r="B487" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C487">
         <v>2050</v>
@@ -51265,7 +51284,7 @@
         <v>161</v>
       </c>
       <c r="E487">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.35">
@@ -51273,7 +51292,7 @@
         <v>73</v>
       </c>
       <c r="B488" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C488">
         <v>2030</v>
@@ -51282,7 +51301,7 @@
         <v>159</v>
       </c>
       <c r="E488">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.35">
@@ -51290,7 +51309,7 @@
         <v>73</v>
       </c>
       <c r="B489" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C489">
         <v>2030</v>
@@ -51299,7 +51318,7 @@
         <v>160</v>
       </c>
       <c r="E489">
-        <v>1</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.35">
@@ -51307,7 +51326,7 @@
         <v>73</v>
       </c>
       <c r="B490" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C490">
         <v>2030</v>
@@ -51316,7 +51335,7 @@
         <v>161</v>
       </c>
       <c r="E490">
-        <v>1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.35">
@@ -51324,7 +51343,7 @@
         <v>73</v>
       </c>
       <c r="B491" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C491">
         <v>2050</v>
@@ -51333,7 +51352,7 @@
         <v>159</v>
       </c>
       <c r="E491">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.35">
@@ -51341,7 +51360,7 @@
         <v>73</v>
       </c>
       <c r="B492" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C492">
         <v>2050</v>
@@ -51350,7 +51369,7 @@
         <v>160</v>
       </c>
       <c r="E492">
-        <v>0.98</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.35">
@@ -51358,7 +51377,7 @@
         <v>73</v>
       </c>
       <c r="B493" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C493">
         <v>2050</v>
@@ -51367,7 +51386,7 @@
         <v>161</v>
       </c>
       <c r="E493">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.35">
@@ -51375,7 +51394,7 @@
         <v>73</v>
       </c>
       <c r="B494" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C494">
         <v>2030</v>
@@ -51392,7 +51411,7 @@
         <v>73</v>
       </c>
       <c r="B495" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C495">
         <v>2030</v>
@@ -51409,7 +51428,7 @@
         <v>73</v>
       </c>
       <c r="B496" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C496">
         <v>2030</v>
@@ -51426,7 +51445,7 @@
         <v>73</v>
       </c>
       <c r="B497" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C497">
         <v>2050</v>
@@ -51443,7 +51462,7 @@
         <v>73</v>
       </c>
       <c r="B498" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C498">
         <v>2050</v>
@@ -51452,7 +51471,7 @@
         <v>160</v>
       </c>
       <c r="E498">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.35">
@@ -51460,7 +51479,7 @@
         <v>73</v>
       </c>
       <c r="B499" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C499">
         <v>2050</v>
@@ -51469,7 +51488,7 @@
         <v>161</v>
       </c>
       <c r="E499">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.35">
@@ -51477,7 +51496,7 @@
         <v>73</v>
       </c>
       <c r="B500" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C500">
         <v>2030</v>
@@ -51494,7 +51513,7 @@
         <v>73</v>
       </c>
       <c r="B501" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C501">
         <v>2030</v>
@@ -51511,7 +51530,7 @@
         <v>73</v>
       </c>
       <c r="B502" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C502">
         <v>2030</v>
@@ -51528,7 +51547,7 @@
         <v>73</v>
       </c>
       <c r="B503" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C503">
         <v>2050</v>
@@ -51545,7 +51564,7 @@
         <v>73</v>
       </c>
       <c r="B504" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C504">
         <v>2050</v>
@@ -51554,7 +51573,7 @@
         <v>160</v>
       </c>
       <c r="E504">
-        <v>1</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.35">
@@ -51562,7 +51581,7 @@
         <v>73</v>
       </c>
       <c r="B505" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C505">
         <v>2050</v>
@@ -51571,7 +51590,7 @@
         <v>161</v>
       </c>
       <c r="E505">
-        <v>1</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.35">
@@ -51579,7 +51598,7 @@
         <v>73</v>
       </c>
       <c r="B506" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C506">
         <v>2030</v>
@@ -51588,7 +51607,7 @@
         <v>159</v>
       </c>
       <c r="E506">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.35">
@@ -51596,7 +51615,7 @@
         <v>73</v>
       </c>
       <c r="B507" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C507">
         <v>2030</v>
@@ -51605,7 +51624,7 @@
         <v>160</v>
       </c>
       <c r="E507">
-        <v>0.93</v>
+        <v>0</v>
       </c>
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.35">
@@ -51613,7 +51632,7 @@
         <v>73</v>
       </c>
       <c r="B508" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C508">
         <v>2030</v>
@@ -51622,7 +51641,7 @@
         <v>161</v>
       </c>
       <c r="E508">
-        <v>0.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.35">
@@ -51630,7 +51649,7 @@
         <v>73</v>
       </c>
       <c r="B509" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C509">
         <v>2050</v>
@@ -51639,7 +51658,7 @@
         <v>159</v>
       </c>
       <c r="E509">
-        <v>0.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.35">
@@ -51647,7 +51666,7 @@
         <v>73</v>
       </c>
       <c r="B510" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C510">
         <v>2050</v>
@@ -51656,7 +51675,7 @@
         <v>160</v>
       </c>
       <c r="E510">
-        <v>0.16</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.35">
@@ -51664,7 +51683,7 @@
         <v>73</v>
       </c>
       <c r="B511" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C511">
         <v>2050</v>
@@ -51673,7 +51692,7 @@
         <v>161</v>
       </c>
       <c r="E511">
-        <v>7.0000000000000007E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.35">
@@ -51681,7 +51700,7 @@
         <v>73</v>
       </c>
       <c r="B512" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C512">
         <v>2030</v>
@@ -51690,7 +51709,7 @@
         <v>159</v>
       </c>
       <c r="E512">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.35">
@@ -51698,7 +51717,7 @@
         <v>73</v>
       </c>
       <c r="B513" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C513">
         <v>2030</v>
@@ -51707,7 +51726,7 @@
         <v>160</v>
       </c>
       <c r="E513">
-        <v>0.06</v>
+        <v>1</v>
       </c>
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.35">
@@ -51715,7 +51734,7 @@
         <v>73</v>
       </c>
       <c r="B514" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C514">
         <v>2030</v>
@@ -51724,7 +51743,7 @@
         <v>161</v>
       </c>
       <c r="E514">
-        <v>0.12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.35">
@@ -51732,7 +51751,7 @@
         <v>73</v>
       </c>
       <c r="B515" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C515">
         <v>2050</v>
@@ -51741,7 +51760,7 @@
         <v>159</v>
       </c>
       <c r="E515">
-        <v>0.05</v>
+        <v>1</v>
       </c>
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.35">
@@ -51749,7 +51768,7 @@
         <v>73</v>
       </c>
       <c r="B516" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C516">
         <v>2050</v>
@@ -51758,7 +51777,7 @@
         <v>160</v>
       </c>
       <c r="E516">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.35">
@@ -51766,7 +51785,7 @@
         <v>73</v>
       </c>
       <c r="B517" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C517">
         <v>2050</v>
@@ -51775,7 +51794,7 @@
         <v>161</v>
       </c>
       <c r="E517">
-        <v>0.92</v>
+        <v>1</v>
       </c>
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.35">
@@ -51783,7 +51802,7 @@
         <v>73</v>
       </c>
       <c r="B518" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C518">
         <v>2030</v>
@@ -51792,7 +51811,7 @@
         <v>159</v>
       </c>
       <c r="E518">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.35">
@@ -51800,7 +51819,7 @@
         <v>73</v>
       </c>
       <c r="B519" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C519">
         <v>2030</v>
@@ -51809,7 +51828,7 @@
         <v>160</v>
       </c>
       <c r="E519">
-        <v>0.01</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.35">
@@ -51817,7 +51836,7 @@
         <v>73</v>
       </c>
       <c r="B520" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C520">
         <v>2030</v>
@@ -51826,7 +51845,7 @@
         <v>161</v>
       </c>
       <c r="E520">
-        <v>0</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.35">
@@ -51834,7 +51853,7 @@
         <v>73</v>
       </c>
       <c r="B521" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C521">
         <v>2050</v>
@@ -51843,7 +51862,7 @@
         <v>159</v>
       </c>
       <c r="E521">
-        <v>0</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.35">
@@ -51851,7 +51870,7 @@
         <v>73</v>
       </c>
       <c r="B522" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C522">
         <v>2050</v>
@@ -51860,7 +51879,7 @@
         <v>160</v>
       </c>
       <c r="E522">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.35">
@@ -51868,7 +51887,7 @@
         <v>73</v>
       </c>
       <c r="B523" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C523">
         <v>2050</v>
@@ -51877,7 +51896,7 @@
         <v>161</v>
       </c>
       <c r="E523">
-        <v>0.01</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.35">
@@ -51885,7 +51904,7 @@
         <v>73</v>
       </c>
       <c r="B524" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C524">
         <v>2030</v>
@@ -51902,7 +51921,7 @@
         <v>73</v>
       </c>
       <c r="B525" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C525">
         <v>2030</v>
@@ -51911,7 +51930,7 @@
         <v>160</v>
       </c>
       <c r="E525">
-        <v>0</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.35">
@@ -51919,7 +51938,7 @@
         <v>73</v>
       </c>
       <c r="B526" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C526">
         <v>2030</v>
@@ -51928,7 +51947,7 @@
         <v>161</v>
       </c>
       <c r="E526">
-        <v>0</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.35">
@@ -51936,7 +51955,7 @@
         <v>73</v>
       </c>
       <c r="B527" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C527">
         <v>2050</v>
@@ -51945,7 +51964,7 @@
         <v>159</v>
       </c>
       <c r="E527">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.35">
@@ -51953,7 +51972,7 @@
         <v>73</v>
       </c>
       <c r="B528" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C528">
         <v>2050</v>
@@ -51962,7 +51981,7 @@
         <v>160</v>
       </c>
       <c r="E528">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.35">
@@ -51970,7 +51989,7 @@
         <v>73</v>
       </c>
       <c r="B529" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C529">
         <v>2050</v>
@@ -51979,7 +51998,7 @@
         <v>161</v>
       </c>
       <c r="E529">
-        <v>0</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.35">
@@ -51987,7 +52006,7 @@
         <v>73</v>
       </c>
       <c r="B530" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C530">
         <v>2030</v>
@@ -51996,7 +52015,7 @@
         <v>159</v>
       </c>
       <c r="E530">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.35">
@@ -52004,7 +52023,7 @@
         <v>73</v>
       </c>
       <c r="B531" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C531">
         <v>2030</v>
@@ -52013,7 +52032,7 @@
         <v>160</v>
       </c>
       <c r="E531">
-        <v>0.93</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.35">
@@ -52021,7 +52040,7 @@
         <v>73</v>
       </c>
       <c r="B532" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C532">
         <v>2030</v>
@@ -52030,7 +52049,7 @@
         <v>161</v>
       </c>
       <c r="E532">
-        <v>0.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.35">
@@ -52038,7 +52057,7 @@
         <v>73</v>
       </c>
       <c r="B533" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C533">
         <v>2050</v>
@@ -52047,7 +52066,7 @@
         <v>159</v>
       </c>
       <c r="E533">
-        <v>0.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.35">
@@ -52055,7 +52074,7 @@
         <v>73</v>
       </c>
       <c r="B534" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C534">
         <v>2050</v>
@@ -52064,7 +52083,7 @@
         <v>160</v>
       </c>
       <c r="E534">
-        <v>0.16</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.35">
@@ -52072,7 +52091,7 @@
         <v>73</v>
       </c>
       <c r="B535" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C535">
         <v>2050</v>
@@ -52081,7 +52100,7 @@
         <v>161</v>
       </c>
       <c r="E535">
-        <v>7.0000000000000007E-2</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.35">
@@ -52089,7 +52108,7 @@
         <v>73</v>
       </c>
       <c r="B536" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C536">
         <v>2030</v>
@@ -52106,7 +52125,7 @@
         <v>73</v>
       </c>
       <c r="B537" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C537">
         <v>2030</v>
@@ -52115,7 +52134,7 @@
         <v>160</v>
       </c>
       <c r="E537">
-        <v>0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.35">
@@ -52123,7 +52142,7 @@
         <v>73</v>
       </c>
       <c r="B538" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C538">
         <v>2030</v>
@@ -52132,7 +52151,7 @@
         <v>161</v>
       </c>
       <c r="E538">
-        <v>0.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.35">
@@ -52140,7 +52159,7 @@
         <v>73</v>
       </c>
       <c r="B539" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C539">
         <v>2050</v>
@@ -52149,7 +52168,7 @@
         <v>159</v>
       </c>
       <c r="E539">
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.35">
@@ -52157,7 +52176,7 @@
         <v>73</v>
       </c>
       <c r="B540" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C540">
         <v>2050</v>
@@ -52166,7 +52185,7 @@
         <v>160</v>
       </c>
       <c r="E540">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.35">
@@ -52174,7 +52193,7 @@
         <v>73</v>
       </c>
       <c r="B541" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C541">
         <v>2050</v>
@@ -52183,7 +52202,7 @@
         <v>161</v>
       </c>
       <c r="E541">
-        <v>0.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.35">
@@ -52191,7 +52210,7 @@
         <v>73</v>
       </c>
       <c r="B542" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C542">
         <v>2030</v>
@@ -52200,7 +52219,7 @@
         <v>159</v>
       </c>
       <c r="E542">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.35">
@@ -52208,7 +52227,7 @@
         <v>73</v>
       </c>
       <c r="B543" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C543">
         <v>2030</v>
@@ -52217,7 +52236,7 @@
         <v>160</v>
       </c>
       <c r="E543">
-        <v>0.01</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.35">
@@ -52225,7 +52244,7 @@
         <v>73</v>
       </c>
       <c r="B544" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C544">
         <v>2030</v>
@@ -52234,7 +52253,7 @@
         <v>161</v>
       </c>
       <c r="E544">
-        <v>0</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.35">
@@ -52242,7 +52261,7 @@
         <v>73</v>
       </c>
       <c r="B545" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C545">
         <v>2050</v>
@@ -52251,7 +52270,7 @@
         <v>159</v>
       </c>
       <c r="E545">
-        <v>0</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.35">
@@ -52259,7 +52278,7 @@
         <v>73</v>
       </c>
       <c r="B546" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C546">
         <v>2050</v>
@@ -52268,7 +52287,7 @@
         <v>160</v>
       </c>
       <c r="E546">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.35">
@@ -52276,7 +52295,7 @@
         <v>73</v>
       </c>
       <c r="B547" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C547">
         <v>2050</v>
@@ -52285,7 +52304,7 @@
         <v>161</v>
       </c>
       <c r="E547">
-        <v>0.01</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.35">
@@ -52293,7 +52312,7 @@
         <v>73</v>
       </c>
       <c r="B548" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C548">
         <v>2030</v>
@@ -52310,7 +52329,7 @@
         <v>73</v>
       </c>
       <c r="B549" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C549">
         <v>2030</v>
@@ -52319,7 +52338,7 @@
         <v>160</v>
       </c>
       <c r="E549">
-        <v>0</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.35">
@@ -52327,7 +52346,7 @@
         <v>73</v>
       </c>
       <c r="B550" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C550">
         <v>2030</v>
@@ -52336,7 +52355,7 @@
         <v>161</v>
       </c>
       <c r="E550">
-        <v>0</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.35">
@@ -52344,7 +52363,7 @@
         <v>73</v>
       </c>
       <c r="B551" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C551">
         <v>2050</v>
@@ -52353,7 +52372,7 @@
         <v>159</v>
       </c>
       <c r="E551">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.35">
@@ -52361,7 +52380,7 @@
         <v>73</v>
       </c>
       <c r="B552" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C552">
         <v>2050</v>
@@ -52370,7 +52389,7 @@
         <v>160</v>
       </c>
       <c r="E552">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.35">
@@ -52378,7 +52397,7 @@
         <v>73</v>
       </c>
       <c r="B553" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C553">
         <v>2050</v>
@@ -52387,7 +52406,7 @@
         <v>161</v>
       </c>
       <c r="E553">
-        <v>0</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.35">
@@ -52395,7 +52414,7 @@
         <v>73</v>
       </c>
       <c r="B554" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C554">
         <v>2030</v>
@@ -52404,7 +52423,7 @@
         <v>159</v>
       </c>
       <c r="E554">
-        <v>0.42199999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.35">
@@ -52412,7 +52431,7 @@
         <v>73</v>
       </c>
       <c r="B555" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C555">
         <v>2030</v>
@@ -52421,7 +52440,7 @@
         <v>160</v>
       </c>
       <c r="E555">
-        <v>0.35</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.35">
@@ -52429,7 +52448,7 @@
         <v>73</v>
       </c>
       <c r="B556" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C556">
         <v>2030</v>
@@ -52438,7 +52457,7 @@
         <v>161</v>
       </c>
       <c r="E556">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.35">
@@ -52446,7 +52465,7 @@
         <v>73</v>
       </c>
       <c r="B557" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C557">
         <v>2050</v>
@@ -52455,7 +52474,7 @@
         <v>159</v>
       </c>
       <c r="E557">
-        <v>0.42199999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.35">
@@ -52463,7 +52482,7 @@
         <v>73</v>
       </c>
       <c r="B558" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C558">
         <v>2050</v>
@@ -52472,7 +52491,7 @@
         <v>160</v>
       </c>
       <c r="E558">
-        <v>0.3</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.35">
@@ -52480,7 +52499,7 @@
         <v>73</v>
       </c>
       <c r="B559" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C559">
         <v>2050</v>
@@ -52489,7 +52508,7 @@
         <v>161</v>
       </c>
       <c r="E559">
-        <v>0.25</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.35">
@@ -52497,7 +52516,7 @@
         <v>73</v>
       </c>
       <c r="B560" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C560">
         <v>2030</v>
@@ -52506,7 +52525,7 @@
         <v>159</v>
       </c>
       <c r="E560">
-        <v>0.57799999999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.35">
@@ -52514,7 +52533,7 @@
         <v>73</v>
       </c>
       <c r="B561" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C561">
         <v>2030</v>
@@ -52523,7 +52542,7 @@
         <v>160</v>
       </c>
       <c r="E561">
-        <v>0.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="562" spans="1:5" x14ac:dyDescent="0.35">
@@ -52531,7 +52550,7 @@
         <v>73</v>
       </c>
       <c r="B562" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C562">
         <v>2030</v>
@@ -52540,7 +52559,7 @@
         <v>161</v>
       </c>
       <c r="E562">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.35">
@@ -52548,7 +52567,7 @@
         <v>73</v>
       </c>
       <c r="B563" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C563">
         <v>2050</v>
@@ -52557,7 +52576,7 @@
         <v>159</v>
       </c>
       <c r="E563">
-        <v>0.57799999999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.35">
@@ -52565,7 +52584,7 @@
         <v>73</v>
       </c>
       <c r="B564" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C564">
         <v>2050</v>
@@ -52574,7 +52593,7 @@
         <v>160</v>
       </c>
       <c r="E564">
-        <v>0.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.35">
@@ -52582,7 +52601,7 @@
         <v>73</v>
       </c>
       <c r="B565" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C565">
         <v>2050</v>
@@ -52591,7 +52610,7 @@
         <v>161</v>
       </c>
       <c r="E565">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.35">
@@ -52599,7 +52618,7 @@
         <v>73</v>
       </c>
       <c r="B566" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C566">
         <v>2030</v>
@@ -52608,7 +52627,7 @@
         <v>159</v>
       </c>
       <c r="E566">
-        <v>0</v>
+        <v>0.42199999999999999</v>
       </c>
     </row>
     <row r="567" spans="1:5" x14ac:dyDescent="0.35">
@@ -52616,7 +52635,7 @@
         <v>73</v>
       </c>
       <c r="B567" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C567">
         <v>2030</v>
@@ -52625,7 +52644,7 @@
         <v>160</v>
       </c>
       <c r="E567">
-        <v>0</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.35">
@@ -52633,7 +52652,7 @@
         <v>73</v>
       </c>
       <c r="B568" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C568">
         <v>2030</v>
@@ -52642,7 +52661,7 @@
         <v>161</v>
       </c>
       <c r="E568">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.35">
@@ -52650,7 +52669,7 @@
         <v>73</v>
       </c>
       <c r="B569" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C569">
         <v>2050</v>
@@ -52659,7 +52678,7 @@
         <v>159</v>
       </c>
       <c r="E569">
-        <v>0</v>
+        <v>0.42199999999999999</v>
       </c>
     </row>
     <row r="570" spans="1:5" x14ac:dyDescent="0.35">
@@ -52667,7 +52686,7 @@
         <v>73</v>
       </c>
       <c r="B570" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C570">
         <v>2050</v>
@@ -52676,7 +52695,7 @@
         <v>160</v>
       </c>
       <c r="E570">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.35">
@@ -52684,7 +52703,7 @@
         <v>73</v>
       </c>
       <c r="B571" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C571">
         <v>2050</v>
@@ -52693,7 +52712,7 @@
         <v>161</v>
       </c>
       <c r="E571">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.35">
@@ -52701,7 +52720,7 @@
         <v>73</v>
       </c>
       <c r="B572" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C572">
         <v>2030</v>
@@ -52710,7 +52729,7 @@
         <v>159</v>
       </c>
       <c r="E572">
-        <v>1</v>
+        <v>0.57799999999999996</v>
       </c>
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.35">
@@ -52718,7 +52737,7 @@
         <v>73</v>
       </c>
       <c r="B573" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C573">
         <v>2030</v>
@@ -52735,7 +52754,7 @@
         <v>73</v>
       </c>
       <c r="B574" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C574">
         <v>2030</v>
@@ -52744,7 +52763,7 @@
         <v>161</v>
       </c>
       <c r="E574">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.35">
@@ -52752,7 +52771,7 @@
         <v>73</v>
       </c>
       <c r="B575" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C575">
         <v>2050</v>
@@ -52761,7 +52780,7 @@
         <v>159</v>
       </c>
       <c r="E575">
-        <v>1</v>
+        <v>0.57799999999999996</v>
       </c>
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.35">
@@ -52769,7 +52788,7 @@
         <v>73</v>
       </c>
       <c r="B576" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C576">
         <v>2050</v>
@@ -52778,7 +52797,7 @@
         <v>160</v>
       </c>
       <c r="E576">
-        <v>0</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.35">
@@ -52786,7 +52805,7 @@
         <v>73</v>
       </c>
       <c r="B577" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C577">
         <v>2050</v>
@@ -52795,7 +52814,7 @@
         <v>161</v>
       </c>
       <c r="E577">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="578" spans="1:5" x14ac:dyDescent="0.35">
@@ -52803,7 +52822,7 @@
         <v>73</v>
       </c>
       <c r="B578" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C578">
         <v>2030</v>
@@ -52820,7 +52839,7 @@
         <v>73</v>
       </c>
       <c r="B579" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C579">
         <v>2030</v>
@@ -52829,7 +52848,7 @@
         <v>160</v>
       </c>
       <c r="E579">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.35">
@@ -52837,7 +52856,7 @@
         <v>73</v>
       </c>
       <c r="B580" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C580">
         <v>2030</v>
@@ -52846,7 +52865,7 @@
         <v>161</v>
       </c>
       <c r="E580">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.35">
@@ -52854,7 +52873,7 @@
         <v>73</v>
       </c>
       <c r="B581" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C581">
         <v>2050</v>
@@ -52871,7 +52890,7 @@
         <v>73</v>
       </c>
       <c r="B582" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C582">
         <v>2050</v>
@@ -52880,7 +52899,7 @@
         <v>160</v>
       </c>
       <c r="E582">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.35">
@@ -52888,7 +52907,7 @@
         <v>73</v>
       </c>
       <c r="B583" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C583">
         <v>2050</v>
@@ -52897,7 +52916,7 @@
         <v>161</v>
       </c>
       <c r="E583">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.35">
@@ -52905,7 +52924,7 @@
         <v>73</v>
       </c>
       <c r="B584" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C584">
         <v>2030</v>
@@ -52914,7 +52933,7 @@
         <v>159</v>
       </c>
       <c r="E584">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="585" spans="1:5" x14ac:dyDescent="0.35">
@@ -52922,7 +52941,7 @@
         <v>73</v>
       </c>
       <c r="B585" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C585">
         <v>2030</v>
@@ -52931,7 +52950,7 @@
         <v>160</v>
       </c>
       <c r="E585">
-        <v>0.1</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="586" spans="1:5" x14ac:dyDescent="0.35">
@@ -52939,7 +52958,7 @@
         <v>73</v>
       </c>
       <c r="B586" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C586">
         <v>2030</v>
@@ -52948,7 +52967,7 @@
         <v>161</v>
       </c>
       <c r="E586">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="587" spans="1:5" x14ac:dyDescent="0.35">
@@ -52956,7 +52975,7 @@
         <v>73</v>
       </c>
       <c r="B587" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C587">
         <v>2050</v>
@@ -52965,7 +52984,7 @@
         <v>159</v>
       </c>
       <c r="E587">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="588" spans="1:5" x14ac:dyDescent="0.35">
@@ -52973,7 +52992,7 @@
         <v>73</v>
       </c>
       <c r="B588" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C588">
         <v>2050</v>
@@ -52982,7 +53001,7 @@
         <v>160</v>
       </c>
       <c r="E588">
-        <v>0.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="589" spans="1:5" x14ac:dyDescent="0.35">
@@ -52990,7 +53009,7 @@
         <v>73</v>
       </c>
       <c r="B589" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C589">
         <v>2050</v>
@@ -52999,7 +53018,7 @@
         <v>161</v>
       </c>
       <c r="E589">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="590" spans="1:5" x14ac:dyDescent="0.35">
@@ -53007,7 +53026,7 @@
         <v>73</v>
       </c>
       <c r="B590" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C590">
         <v>2030</v>
@@ -53024,7 +53043,7 @@
         <v>73</v>
       </c>
       <c r="B591" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C591">
         <v>2030</v>
@@ -53033,7 +53052,7 @@
         <v>160</v>
       </c>
       <c r="E591">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="592" spans="1:5" x14ac:dyDescent="0.35">
@@ -53041,7 +53060,7 @@
         <v>73</v>
       </c>
       <c r="B592" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C592">
         <v>2030</v>
@@ -53050,7 +53069,7 @@
         <v>161</v>
       </c>
       <c r="E592">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="593" spans="1:5" x14ac:dyDescent="0.35">
@@ -53058,7 +53077,7 @@
         <v>73</v>
       </c>
       <c r="B593" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C593">
         <v>2050</v>
@@ -53075,7 +53094,7 @@
         <v>73</v>
       </c>
       <c r="B594" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C594">
         <v>2050</v>
@@ -53084,7 +53103,7 @@
         <v>160</v>
       </c>
       <c r="E594">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.35">
@@ -53092,7 +53111,7 @@
         <v>73</v>
       </c>
       <c r="B595" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C595">
         <v>2050</v>
@@ -53101,7 +53120,7 @@
         <v>161</v>
       </c>
       <c r="E595">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.35">
@@ -53109,7 +53128,7 @@
         <v>73</v>
       </c>
       <c r="B596" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C596">
         <v>2030</v>
@@ -53126,7 +53145,7 @@
         <v>73</v>
       </c>
       <c r="B597" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C597">
         <v>2030</v>
@@ -53135,7 +53154,7 @@
         <v>160</v>
       </c>
       <c r="E597">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="598" spans="1:5" x14ac:dyDescent="0.35">
@@ -53143,7 +53162,7 @@
         <v>73</v>
       </c>
       <c r="B598" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C598">
         <v>2030</v>
@@ -53152,7 +53171,7 @@
         <v>161</v>
       </c>
       <c r="E598">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.35">
@@ -53160,7 +53179,7 @@
         <v>73</v>
       </c>
       <c r="B599" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C599">
         <v>2050</v>
@@ -53177,7 +53196,7 @@
         <v>73</v>
       </c>
       <c r="B600" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C600">
         <v>2050</v>
@@ -53186,7 +53205,7 @@
         <v>160</v>
       </c>
       <c r="E600">
-        <v>0.15</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="601" spans="1:5" x14ac:dyDescent="0.35">
@@ -53194,7 +53213,7 @@
         <v>73</v>
       </c>
       <c r="B601" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C601">
         <v>2050</v>
@@ -53203,7 +53222,7 @@
         <v>161</v>
       </c>
       <c r="E601">
-        <v>0.02</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="602" spans="1:5" x14ac:dyDescent="0.35">
@@ -53211,7 +53230,7 @@
         <v>73</v>
       </c>
       <c r="B602" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C602">
         <v>2030</v>
@@ -53220,7 +53239,7 @@
         <v>159</v>
       </c>
       <c r="E602">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="603" spans="1:5" x14ac:dyDescent="0.35">
@@ -53228,7 +53247,7 @@
         <v>73</v>
       </c>
       <c r="B603" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C603">
         <v>2030</v>
@@ -53237,7 +53256,7 @@
         <v>160</v>
       </c>
       <c r="E603">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="604" spans="1:5" x14ac:dyDescent="0.35">
@@ -53245,7 +53264,7 @@
         <v>73</v>
       </c>
       <c r="B604" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C604">
         <v>2030</v>
@@ -53254,7 +53273,7 @@
         <v>161</v>
       </c>
       <c r="E604">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="605" spans="1:5" x14ac:dyDescent="0.35">
@@ -53262,7 +53281,7 @@
         <v>73</v>
       </c>
       <c r="B605" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C605">
         <v>2050</v>
@@ -53271,7 +53290,7 @@
         <v>159</v>
       </c>
       <c r="E605">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.35">
@@ -53279,7 +53298,7 @@
         <v>73</v>
       </c>
       <c r="B606" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C606">
         <v>2050</v>
@@ -53288,7 +53307,7 @@
         <v>160</v>
       </c>
       <c r="E606">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="607" spans="1:5" x14ac:dyDescent="0.35">
@@ -53296,7 +53315,7 @@
         <v>73</v>
       </c>
       <c r="B607" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C607">
         <v>2050</v>
@@ -53305,7 +53324,7 @@
         <v>161</v>
       </c>
       <c r="E607">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="608" spans="1:5" x14ac:dyDescent="0.35">
@@ -53313,7 +53332,7 @@
         <v>73</v>
       </c>
       <c r="B608" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C608">
         <v>2030</v>
@@ -53322,7 +53341,7 @@
         <v>159</v>
       </c>
       <c r="E608">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="609" spans="1:5" x14ac:dyDescent="0.35">
@@ -53330,7 +53349,7 @@
         <v>73</v>
       </c>
       <c r="B609" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C609">
         <v>2030</v>
@@ -53339,7 +53358,7 @@
         <v>160</v>
       </c>
       <c r="E609">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="610" spans="1:5" x14ac:dyDescent="0.35">
@@ -53347,7 +53366,7 @@
         <v>73</v>
       </c>
       <c r="B610" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C610">
         <v>2030</v>
@@ -53356,7 +53375,7 @@
         <v>161</v>
       </c>
       <c r="E610">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="611" spans="1:5" x14ac:dyDescent="0.35">
@@ -53364,7 +53383,7 @@
         <v>73</v>
       </c>
       <c r="B611" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C611">
         <v>2050</v>
@@ -53373,7 +53392,7 @@
         <v>159</v>
       </c>
       <c r="E611">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="612" spans="1:5" x14ac:dyDescent="0.35">
@@ -53381,7 +53400,7 @@
         <v>73</v>
       </c>
       <c r="B612" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C612">
         <v>2050</v>
@@ -53390,7 +53409,7 @@
         <v>160</v>
       </c>
       <c r="E612">
-        <v>1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.35">
@@ -53398,7 +53417,7 @@
         <v>73</v>
       </c>
       <c r="B613" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C613">
         <v>2050</v>
@@ -53407,7 +53426,7 @@
         <v>161</v>
       </c>
       <c r="E613">
-        <v>1</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.35">
@@ -53415,7 +53434,7 @@
         <v>73</v>
       </c>
       <c r="B614" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C614">
         <v>2030</v>
@@ -53424,7 +53443,7 @@
         <v>159</v>
       </c>
       <c r="E614">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="615" spans="1:5" x14ac:dyDescent="0.35">
@@ -53432,7 +53451,7 @@
         <v>73</v>
       </c>
       <c r="B615" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C615">
         <v>2030</v>
@@ -53441,7 +53460,7 @@
         <v>160</v>
       </c>
       <c r="E615">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="616" spans="1:5" x14ac:dyDescent="0.35">
@@ -53449,7 +53468,7 @@
         <v>73</v>
       </c>
       <c r="B616" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C616">
         <v>2030</v>
@@ -53458,7 +53477,7 @@
         <v>161</v>
       </c>
       <c r="E616">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="617" spans="1:5" x14ac:dyDescent="0.35">
@@ -53466,7 +53485,7 @@
         <v>73</v>
       </c>
       <c r="B617" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C617">
         <v>2050</v>
@@ -53475,7 +53494,7 @@
         <v>159</v>
       </c>
       <c r="E617">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="618" spans="1:5" x14ac:dyDescent="0.35">
@@ -53483,7 +53502,7 @@
         <v>73</v>
       </c>
       <c r="B618" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C618">
         <v>2050</v>
@@ -53492,7 +53511,7 @@
         <v>160</v>
       </c>
       <c r="E618">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="619" spans="1:5" x14ac:dyDescent="0.35">
@@ -53500,7 +53519,7 @@
         <v>73</v>
       </c>
       <c r="B619" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C619">
         <v>2050</v>
@@ -53509,7 +53528,7 @@
         <v>161</v>
       </c>
       <c r="E619">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="620" spans="1:5" x14ac:dyDescent="0.35">
@@ -53517,7 +53536,7 @@
         <v>73</v>
       </c>
       <c r="B620" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C620">
         <v>2030</v>
@@ -53526,7 +53545,7 @@
         <v>159</v>
       </c>
       <c r="E620">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="621" spans="1:5" x14ac:dyDescent="0.35">
@@ -53534,7 +53553,7 @@
         <v>73</v>
       </c>
       <c r="B621" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C621">
         <v>2030</v>
@@ -53543,7 +53562,7 @@
         <v>160</v>
       </c>
       <c r="E621">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="622" spans="1:5" x14ac:dyDescent="0.35">
@@ -53551,7 +53570,7 @@
         <v>73</v>
       </c>
       <c r="B622" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C622">
         <v>2030</v>
@@ -53560,7 +53579,7 @@
         <v>161</v>
       </c>
       <c r="E622">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="623" spans="1:5" x14ac:dyDescent="0.35">
@@ -53568,7 +53587,7 @@
         <v>73</v>
       </c>
       <c r="B623" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C623">
         <v>2050</v>
@@ -53577,7 +53596,7 @@
         <v>159</v>
       </c>
       <c r="E623">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="624" spans="1:5" x14ac:dyDescent="0.35">
@@ -53585,7 +53604,7 @@
         <v>73</v>
       </c>
       <c r="B624" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C624">
         <v>2050</v>
@@ -53594,7 +53613,7 @@
         <v>160</v>
       </c>
       <c r="E624">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="625" spans="1:5" x14ac:dyDescent="0.35">
@@ -53602,7 +53621,7 @@
         <v>73</v>
       </c>
       <c r="B625" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C625">
         <v>2050</v>
@@ -53611,7 +53630,7 @@
         <v>161</v>
       </c>
       <c r="E625">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="626" spans="1:5" x14ac:dyDescent="0.35">
@@ -53619,7 +53638,7 @@
         <v>73</v>
       </c>
       <c r="B626" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C626">
         <v>2030</v>
@@ -53636,7 +53655,7 @@
         <v>73</v>
       </c>
       <c r="B627" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C627">
         <v>2030</v>
@@ -53653,7 +53672,7 @@
         <v>73</v>
       </c>
       <c r="B628" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C628">
         <v>2030</v>
@@ -53670,7 +53689,7 @@
         <v>73</v>
       </c>
       <c r="B629" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C629">
         <v>2050</v>
@@ -53687,7 +53706,7 @@
         <v>73</v>
       </c>
       <c r="B630" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C630">
         <v>2050</v>
@@ -53704,7 +53723,7 @@
         <v>73</v>
       </c>
       <c r="B631" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C631">
         <v>2050</v>
@@ -53721,7 +53740,7 @@
         <v>73</v>
       </c>
       <c r="B632" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C632">
         <v>2030</v>
@@ -53738,7 +53757,7 @@
         <v>73</v>
       </c>
       <c r="B633" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C633">
         <v>2030</v>
@@ -53747,7 +53766,7 @@
         <v>160</v>
       </c>
       <c r="E633">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="634" spans="1:5" x14ac:dyDescent="0.35">
@@ -53755,7 +53774,7 @@
         <v>73</v>
       </c>
       <c r="B634" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C634">
         <v>2030</v>
@@ -53764,7 +53783,7 @@
         <v>161</v>
       </c>
       <c r="E634">
-        <v>0.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="635" spans="1:5" x14ac:dyDescent="0.35">
@@ -53772,7 +53791,7 @@
         <v>73</v>
       </c>
       <c r="B635" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C635">
         <v>2050</v>
@@ -53789,7 +53808,7 @@
         <v>73</v>
       </c>
       <c r="B636" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C636">
         <v>2050</v>
@@ -53798,7 +53817,7 @@
         <v>160</v>
       </c>
       <c r="E636">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="637" spans="1:5" x14ac:dyDescent="0.35">
@@ -53806,7 +53825,7 @@
         <v>73</v>
       </c>
       <c r="B637" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C637">
         <v>2050</v>
@@ -53815,7 +53834,7 @@
         <v>161</v>
       </c>
       <c r="E637">
-        <v>0.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="638" spans="1:5" x14ac:dyDescent="0.35">
@@ -53823,7 +53842,7 @@
         <v>73</v>
       </c>
       <c r="B638" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C638">
         <v>2030</v>
@@ -53840,7 +53859,7 @@
         <v>73</v>
       </c>
       <c r="B639" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C639">
         <v>2030</v>
@@ -53849,7 +53868,7 @@
         <v>160</v>
       </c>
       <c r="E639">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="640" spans="1:5" x14ac:dyDescent="0.35">
@@ -53857,7 +53876,7 @@
         <v>73</v>
       </c>
       <c r="B640" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C640">
         <v>2030</v>
@@ -53866,7 +53885,7 @@
         <v>161</v>
       </c>
       <c r="E640">
-        <v>0.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="641" spans="1:5" x14ac:dyDescent="0.35">
@@ -53874,7 +53893,7 @@
         <v>73</v>
       </c>
       <c r="B641" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C641">
         <v>2050</v>
@@ -53891,7 +53910,7 @@
         <v>73</v>
       </c>
       <c r="B642" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C642">
         <v>2050</v>
@@ -53900,7 +53919,7 @@
         <v>160</v>
       </c>
       <c r="E642">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="643" spans="1:5" x14ac:dyDescent="0.35">
@@ -53908,7 +53927,7 @@
         <v>73</v>
       </c>
       <c r="B643" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C643">
         <v>2050</v>
@@ -53917,7 +53936,7 @@
         <v>161</v>
       </c>
       <c r="E643">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="644" spans="1:5" x14ac:dyDescent="0.35">
@@ -53925,7 +53944,7 @@
         <v>73</v>
       </c>
       <c r="B644" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C644">
         <v>2030</v>
@@ -53934,7 +53953,7 @@
         <v>159</v>
       </c>
       <c r="E644">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="645" spans="1:5" x14ac:dyDescent="0.35">
@@ -53942,7 +53961,7 @@
         <v>73</v>
       </c>
       <c r="B645" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C645">
         <v>2030</v>
@@ -53951,7 +53970,7 @@
         <v>160</v>
       </c>
       <c r="E645">
-        <v>0.5</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="646" spans="1:5" x14ac:dyDescent="0.35">
@@ -53959,7 +53978,7 @@
         <v>73</v>
       </c>
       <c r="B646" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C646">
         <v>2030</v>
@@ -53968,7 +53987,7 @@
         <v>161</v>
       </c>
       <c r="E646">
-        <v>0.5</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="647" spans="1:5" x14ac:dyDescent="0.35">
@@ -53976,7 +53995,7 @@
         <v>73</v>
       </c>
       <c r="B647" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C647">
         <v>2050</v>
@@ -53985,7 +54004,7 @@
         <v>159</v>
       </c>
       <c r="E647">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="648" spans="1:5" x14ac:dyDescent="0.35">
@@ -53993,7 +54012,7 @@
         <v>73</v>
       </c>
       <c r="B648" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C648">
         <v>2050</v>
@@ -54002,7 +54021,7 @@
         <v>160</v>
       </c>
       <c r="E648">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="649" spans="1:5" x14ac:dyDescent="0.35">
@@ -54010,7 +54029,7 @@
         <v>73</v>
       </c>
       <c r="B649" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C649">
         <v>2050</v>
@@ -54019,6 +54038,210 @@
         <v>161</v>
       </c>
       <c r="E649">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="650" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A650" t="s">
+        <v>73</v>
+      </c>
+      <c r="B650" t="s">
+        <v>157</v>
+      </c>
+      <c r="C650">
+        <v>2030</v>
+      </c>
+      <c r="D650" t="s">
+        <v>159</v>
+      </c>
+      <c r="E650">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="651" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A651" t="s">
+        <v>73</v>
+      </c>
+      <c r="B651" t="s">
+        <v>157</v>
+      </c>
+      <c r="C651">
+        <v>2030</v>
+      </c>
+      <c r="D651" t="s">
+        <v>160</v>
+      </c>
+      <c r="E651">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="652" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A652" t="s">
+        <v>73</v>
+      </c>
+      <c r="B652" t="s">
+        <v>157</v>
+      </c>
+      <c r="C652">
+        <v>2030</v>
+      </c>
+      <c r="D652" t="s">
+        <v>161</v>
+      </c>
+      <c r="E652">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="653" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A653" t="s">
+        <v>73</v>
+      </c>
+      <c r="B653" t="s">
+        <v>157</v>
+      </c>
+      <c r="C653">
+        <v>2050</v>
+      </c>
+      <c r="D653" t="s">
+        <v>159</v>
+      </c>
+      <c r="E653">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="654" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A654" t="s">
+        <v>73</v>
+      </c>
+      <c r="B654" t="s">
+        <v>157</v>
+      </c>
+      <c r="C654">
+        <v>2050</v>
+      </c>
+      <c r="D654" t="s">
+        <v>160</v>
+      </c>
+      <c r="E654">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="655" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A655" t="s">
+        <v>73</v>
+      </c>
+      <c r="B655" t="s">
+        <v>157</v>
+      </c>
+      <c r="C655">
+        <v>2050</v>
+      </c>
+      <c r="D655" t="s">
+        <v>161</v>
+      </c>
+      <c r="E655">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="656" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A656" t="s">
+        <v>73</v>
+      </c>
+      <c r="B656" t="s">
+        <v>158</v>
+      </c>
+      <c r="C656">
+        <v>2030</v>
+      </c>
+      <c r="D656" t="s">
+        <v>159</v>
+      </c>
+      <c r="E656">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="657" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A657" t="s">
+        <v>73</v>
+      </c>
+      <c r="B657" t="s">
+        <v>158</v>
+      </c>
+      <c r="C657">
+        <v>2030</v>
+      </c>
+      <c r="D657" t="s">
+        <v>160</v>
+      </c>
+      <c r="E657">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="658" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A658" t="s">
+        <v>73</v>
+      </c>
+      <c r="B658" t="s">
+        <v>158</v>
+      </c>
+      <c r="C658">
+        <v>2030</v>
+      </c>
+      <c r="D658" t="s">
+        <v>161</v>
+      </c>
+      <c r="E658">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="659" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A659" t="s">
+        <v>73</v>
+      </c>
+      <c r="B659" t="s">
+        <v>158</v>
+      </c>
+      <c r="C659">
+        <v>2050</v>
+      </c>
+      <c r="D659" t="s">
+        <v>159</v>
+      </c>
+      <c r="E659">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="660" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A660" t="s">
+        <v>73</v>
+      </c>
+      <c r="B660" t="s">
+        <v>158</v>
+      </c>
+      <c r="C660">
+        <v>2050</v>
+      </c>
+      <c r="D660" t="s">
+        <v>160</v>
+      </c>
+      <c r="E660">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="661" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A661" t="s">
+        <v>73</v>
+      </c>
+      <c r="B661" t="s">
+        <v>158</v>
+      </c>
+      <c r="C661">
+        <v>2050</v>
+      </c>
+      <c r="D661" t="s">
+        <v>161</v>
+      </c>
+      <c r="E661">
         <v>0.5</v>
       </c>
     </row>

--- a/transport/trans_config.xlsx
+++ b/transport/trans_config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fraunhofer-my.sharepoint.com/personal/rakesh_etikala_narendar_iee_fraunhofer_de/Documents/Desktop/sectoral-energy-demands/transport/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="205" documentId="11_23F921EDAE034F2B492C4C492D40CC9F4213A6C0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3458ECFF-A4F2-48C7-972E-731BE5BA7BAD}"/>
+  <xr:revisionPtr revIDLastSave="213" documentId="11_23F921EDAE034F2B492C4C492D40CC9F4213A6C0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91591F53-433F-41E3-9B2F-D670405760AB}"/>
   <bookViews>
-    <workbookView xWindow="19910" yWindow="1770" windowWidth="18450" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7380" yWindow="3810" windowWidth="30760" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -904,8 +904,10 @@
     <col min="1" max="1" width="15.36328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="45.6328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.7265625" customWidth="1"/>
-    <col min="27" max="27" width="11" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="26" width="0" hidden="1" customWidth="1"/>
+    <col min="27" max="27" width="11" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="11.08984375" hidden="1" customWidth="1"/>
+    <col min="29" max="30" width="0" hidden="1" customWidth="1"/>
     <col min="35" max="35" width="11.54296875" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="9.54296875" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="21.08984375" bestFit="1" customWidth="1"/>
@@ -52256,7 +52258,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="545" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
         <v>73</v>
       </c>
@@ -52273,7 +52275,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="546" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
         <v>73</v>
       </c>
@@ -52290,7 +52292,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="547" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
         <v>73</v>
       </c>
@@ -52306,8 +52308,11 @@
       <c r="E547">
         <v>7.0000000000000007E-2</v>
       </c>
-    </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="AE547">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
         <v>73</v>
       </c>
@@ -52324,7 +52329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
         <v>73</v>
       </c>
@@ -52341,7 +52346,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="550" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
         <v>73</v>
       </c>
@@ -52358,7 +52363,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="551" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
         <v>73</v>
       </c>
@@ -52375,7 +52380,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="552" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
         <v>73</v>
       </c>
@@ -52392,7 +52397,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="553" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
         <v>73</v>
       </c>
@@ -52408,8 +52413,11 @@
       <c r="E553">
         <v>0.92</v>
       </c>
-    </row>
-    <row r="554" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="AE553">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="554" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
         <v>73</v>
       </c>
@@ -52426,7 +52434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="555" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
         <v>73</v>
       </c>
@@ -52443,7 +52451,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="556" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
         <v>73</v>
       </c>
@@ -52460,7 +52468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="557" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
         <v>73</v>
       </c>
@@ -52477,7 +52485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="558" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
         <v>73</v>
       </c>
@@ -52494,7 +52502,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="559" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
         <v>73</v>
       </c>
@@ -52510,8 +52518,11 @@
       <c r="E559">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="560" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="AE559">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="560" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
         <v>73</v>
       </c>
@@ -52800,7 +52811,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="577" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
         <v>73</v>
       </c>
@@ -52817,7 +52828,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="578" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
         <v>73</v>
       </c>
@@ -52834,7 +52845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="579" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
         <v>73</v>
       </c>
@@ -52851,7 +52862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="580" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
         <v>73</v>
       </c>
@@ -52868,7 +52879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="581" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
         <v>73</v>
       </c>
@@ -52885,7 +52896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="582" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
         <v>73</v>
       </c>
@@ -52902,7 +52913,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="583" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
         <v>73</v>
       </c>
@@ -52919,7 +52930,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="584" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
         <v>73</v>
       </c>
@@ -52936,7 +52947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="585" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
         <v>73</v>
       </c>
@@ -52953,7 +52964,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="586" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
         <v>73</v>
       </c>
@@ -52970,7 +52981,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="587" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
         <v>73</v>
       </c>
@@ -52987,7 +52998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="588" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
         <v>73</v>
       </c>
@@ -53004,7 +53015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="589" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
         <v>73</v>
       </c>
@@ -53020,8 +53031,11 @@
       <c r="E589">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="590" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="AE589">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="590" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
         <v>73</v>
       </c>
@@ -53038,7 +53052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="591" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
         <v>73</v>
       </c>
@@ -53055,7 +53069,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="592" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
         <v>73</v>
       </c>
@@ -53072,7 +53086,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="593" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
         <v>73</v>
       </c>
@@ -53089,7 +53103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="594" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
         <v>73</v>
       </c>
@@ -53106,7 +53120,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="595" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
         <v>73</v>
       </c>
@@ -53123,7 +53137,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="596" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
         <v>73</v>
       </c>
@@ -53140,7 +53154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="597" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
         <v>73</v>
       </c>
@@ -53157,7 +53171,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="598" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
         <v>73</v>
       </c>
@@ -53174,7 +53188,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="599" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
         <v>73</v>
       </c>
@@ -53191,7 +53205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="600" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
         <v>73</v>
       </c>
@@ -53208,7 +53222,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="601" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
         <v>73</v>
       </c>
@@ -53224,8 +53238,11 @@
       <c r="E601">
         <v>0.38</v>
       </c>
-    </row>
-    <row r="602" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="AE601">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="602" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
         <v>73</v>
       </c>
@@ -53242,7 +53259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="603" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
         <v>73</v>
       </c>
@@ -53259,7 +53276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="604" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
         <v>73</v>
       </c>
@@ -53276,7 +53293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="605" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
         <v>73</v>
       </c>
@@ -53293,7 +53310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="606" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
         <v>73</v>
       </c>
@@ -53310,7 +53327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="607" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
         <v>73</v>
       </c>
@@ -53327,7 +53344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="608" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
         <v>73</v>
       </c>
@@ -53344,7 +53361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="609" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
         <v>73</v>
       </c>
@@ -53361,7 +53378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="610" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
         <v>73</v>
       </c>
@@ -53378,7 +53395,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="611" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
         <v>73</v>
       </c>
@@ -53395,7 +53412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="612" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
         <v>73</v>
       </c>
@@ -53412,7 +53429,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="613" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
         <v>73</v>
       </c>
@@ -53428,8 +53445,11 @@
       <c r="E613">
         <v>0.02</v>
       </c>
-    </row>
-    <row r="614" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="AE613">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="614" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
         <v>73</v>
       </c>
@@ -53446,7 +53466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="615" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
         <v>73</v>
       </c>
@@ -53463,7 +53483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="616" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
         <v>73</v>
       </c>
@@ -53480,7 +53500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="617" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
         <v>73</v>
       </c>
@@ -53497,7 +53517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="618" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
         <v>73</v>
       </c>
@@ -53514,7 +53534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="619" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
         <v>73</v>
       </c>
@@ -53531,7 +53551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="620" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
         <v>73</v>
       </c>
@@ -53548,7 +53568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="621" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
         <v>73</v>
       </c>
@@ -53565,7 +53585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="622" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
         <v>73</v>
       </c>
@@ -53582,7 +53602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="623" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
         <v>73</v>
       </c>
@@ -53599,7 +53619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="624" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
         <v>73</v>
       </c>
@@ -53888,7 +53908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="641" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
         <v>73</v>
       </c>
@@ -53905,7 +53925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="642" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
         <v>73</v>
       </c>
@@ -53922,7 +53942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="643" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
         <v>73</v>
       </c>
@@ -53939,7 +53959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="644" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
         <v>73</v>
       </c>
@@ -53956,7 +53976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="645" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
         <v>73</v>
       </c>
@@ -53973,7 +53993,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="646" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
         <v>73</v>
       </c>
@@ -53990,7 +54010,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="647" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
         <v>73</v>
       </c>
@@ -54007,7 +54027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="648" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
         <v>73</v>
       </c>
@@ -54024,7 +54044,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="649" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
         <v>73</v>
       </c>
@@ -54041,7 +54061,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="650" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
         <v>73</v>
       </c>
@@ -54058,7 +54078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="651" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
         <v>73</v>
       </c>
@@ -54075,7 +54095,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="652" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
         <v>73</v>
       </c>
@@ -54092,7 +54112,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="653" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
         <v>73</v>
       </c>
@@ -54109,7 +54129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="654" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
         <v>73</v>
       </c>
@@ -54126,7 +54146,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="655" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
         <v>73</v>
       </c>
@@ -54142,8 +54162,11 @@
       <c r="E655">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="656" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="AE655">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="656" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A656" t="s">
         <v>73</v>
       </c>

--- a/transport/trans_config.xlsx
+++ b/transport/trans_config.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="347" documentId="11_23F921EDAE034F2B492C4C492D40CC9F4213A6C0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6416FC3-13BB-4F7C-9F26-98558DEE2955}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14940" yWindow="1070" windowWidth="20320" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
